--- a/backend/data/exports/reports/output/executive_summary.xlsx
+++ b/backend/data/exports/reports/output/executive_summary.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[{"Insight": "Highest loss category", "Value": "Low"}, {"Insight": "Most delayed route", "Value": "RTE-9810A785"}, {"Insight": "Most affected product", "Value": "Frozen French Fries"}, {"Insight": "Most affected city", "Value": "Jaipur"}, {"Insight": "Most affected transport mode", "Value": "Sea"}, {"Insight": "Top insurance claims (Origin-&gt;Destination)", "Value": "[{\"Origin City\": \"Bhubaneswar\", \"Destination City\": \"Gurugram\", \"Total Insurance Claim Amount\": 251969.5199999998}, {\"Origin City\": \"Ahmedabad\", \"Destination City\": \"Kochi\", \"Total Insurance Claim Amount\": 234142.12799999985}, {\"Origin City\": \"Chennai\", \"Destination City\": \"Visakhapatnam\", \"Total Insurance Claim Amount\": 192026.2739999998}, {\"Origin City\": \"Srinagar\", \"Destination City\": \"Chennai\", \"Total Insurance Claim Amount\": 186592.38399999985}, {\"Origin City\": \"Srinagar\", \"Destination City\": \"Pune\", \"Total Insurance Claim Amount\": 170290.5599999998}]"}, {"Insight": "Recovery opportunities (Origin-&gt;Destination)", "Value": "[{\"Origin City\": \"Bhubaneswar\", \"Destination City\": \"Gurugram\", \"Total Recovery Amount\": 251969.5199999998}, {\"Origin City\": \"Ahmedabad\", \"Destination City\": \"Kochi\", \"Total Recovery Amount\": 242664.87999999957}, {\"Origin City\": \"Srinagar\", \"Destination City\": \"Chennai\", \"Total Recovery Amount\": 197811.36799999975}, {\"Origin City\": \"Chennai\", \"Destination City\": \"Visakhapatnam\", \"Total Recovery Amount\": 192026.2739999998}, {\"Origin City\": \"Pune\", \"Destination City\": \"Chandigarh\", \"Total Recovery Amount\": 177586.5839999997}]"}, {"Insight": "Operational performance (Cold chain compliance %)", "Value": 79.62555066079295}, {"Insight": "Business health (Loss fraction of inventory)", "Value": 0.1062097488837984}, {"Insight": "Risk distribution", "Value": "{\"Medium Risk\": 595, \"Low Risk\": 176, \"High Risk\": 136, \"Critical Risk\": 1}"}, {"Insight": "Insurance threshold (Loss fraction)", "Value": 0.15}, {"Insight": "Recovery threshold (Loss fraction)", "Value": 0.07}]</t>
+          <t>[{"Insight": "Highest loss category", "Value": "Low"}, {"Insight": "Most delayed route", "Value": "RTE-7F91720C"}, {"Insight": "Most affected product", "Value": "Frozen French Fries"}, {"Insight": "Most affected city", "Value": "Jaipur"}, {"Insight": "Most affected transport mode", "Value": "Sea"}, {"Insight": "Top insurance claims (Origin-&gt;Destination)", "Value": "[{\"Origin City\": \"Bhubaneswar\", \"Destination City\": \"Gurugram\", \"Total Insurance Claim Amount\": 251969.5199999998}, {\"Origin City\": \"Ahmedabad\", \"Destination City\": \"Kochi\", \"Total Insurance Claim Amount\": 234142.12799999985}, {\"Origin City\": \"Chennai\", \"Destination City\": \"Visakhapatnam\", \"Total Insurance Claim Amount\": 192026.2739999998}, {\"Origin City\": \"Srinagar\", \"Destination City\": \"Chennai\", \"Total Insurance Claim Amount\": 186592.38399999985}, {\"Origin City\": \"Srinagar\", \"Destination City\": \"Pune\", \"Total Insurance Claim Amount\": 170290.5599999998}]"}, {"Insight": "Recovery opportunities (Origin-&gt;Destination)", "Value": "[{\"Origin City\": \"Bhubaneswar\", \"Destination City\": \"Gurugram\", \"Total Recovery Amount\": 251969.5199999998}, {\"Origin City\": \"Ahmedabad\", \"Destination City\": \"Kochi\", \"Total Recovery Amount\": 242664.87999999957}, {\"Origin City\": \"Srinagar\", \"Destination City\": \"Chennai\", \"Total Recovery Amount\": 197811.36799999975}, {\"Origin City\": \"Chennai\", \"Destination City\": \"Visakhapatnam\", \"Total Recovery Amount\": 192026.2739999998}, {\"Origin City\": \"Pune\", \"Destination City\": \"Chandigarh\", \"Total Recovery Amount\": 177586.5839999997}]"}, {"Insight": "Operational performance (Cold chain compliance %)", "Value": 79.62555066079295}, {"Insight": "Business health (Loss fraction of inventory)", "Value": 0.1062097488837984}, {"Insight": "Risk distribution", "Value": "{\"Medium Risk\": 595, \"Low Risk\": 176, \"High Risk\": 136, \"Critical Risk\": 1}"}, {"Insight": "Insurance threshold (Loss fraction)", "Value": 0.15}, {"Insight": "Recovery threshold (Loss fraction)", "Value": 0.07}]</t>
         </is>
       </c>
     </row>

--- a/backend/data/exports/reports/output/executive_summary.xlsx
+++ b/backend/data/exports/reports/output/executive_summary.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[{"Insight": "Highest loss category", "Value": "Low"}, {"Insight": "Most delayed route", "Value": "RTE-7F91720C"}, {"Insight": "Most affected product", "Value": "Frozen French Fries"}, {"Insight": "Most affected city", "Value": "Jaipur"}, {"Insight": "Most affected transport mode", "Value": "Sea"}, {"Insight": "Top insurance claims (Origin-&gt;Destination)", "Value": "[{\"Origin City\": \"Bhubaneswar\", \"Destination City\": \"Gurugram\", \"Total Insurance Claim Amount\": 251969.5199999998}, {\"Origin City\": \"Ahmedabad\", \"Destination City\": \"Kochi\", \"Total Insurance Claim Amount\": 234142.12799999985}, {\"Origin City\": \"Chennai\", \"Destination City\": \"Visakhapatnam\", \"Total Insurance Claim Amount\": 192026.2739999998}, {\"Origin City\": \"Srinagar\", \"Destination City\": \"Chennai\", \"Total Insurance Claim Amount\": 186592.38399999985}, {\"Origin City\": \"Srinagar\", \"Destination City\": \"Pune\", \"Total Insurance Claim Amount\": 170290.5599999998}]"}, {"Insight": "Recovery opportunities (Origin-&gt;Destination)", "Value": "[{\"Origin City\": \"Bhubaneswar\", \"Destination City\": \"Gurugram\", \"Total Recovery Amount\": 251969.5199999998}, {\"Origin City\": \"Ahmedabad\", \"Destination City\": \"Kochi\", \"Total Recovery Amount\": 242664.87999999957}, {\"Origin City\": \"Srinagar\", \"Destination City\": \"Chennai\", \"Total Recovery Amount\": 197811.36799999975}, {\"Origin City\": \"Chennai\", \"Destination City\": \"Visakhapatnam\", \"Total Recovery Amount\": 192026.2739999998}, {\"Origin City\": \"Pune\", \"Destination City\": \"Chandigarh\", \"Total Recovery Amount\": 177586.5839999997}]"}, {"Insight": "Operational performance (Cold chain compliance %)", "Value": 79.62555066079295}, {"Insight": "Business health (Loss fraction of inventory)", "Value": 0.1062097488837984}, {"Insight": "Risk distribution", "Value": "{\"Medium Risk\": 595, \"Low Risk\": 176, \"High Risk\": 136, \"Critical Risk\": 1}"}, {"Insight": "Insurance threshold (Loss fraction)", "Value": 0.15}, {"Insight": "Recovery threshold (Loss fraction)", "Value": 0.07}]</t>
+          <t>[{"Insight": "Highest loss category", "Value": "Low"}, {"Insight": "Most delayed route", "Value": "RTE-D73A13D7"}, {"Insight": "Most affected product", "Value": "Frozen French Fries"}, {"Insight": "Most affected city", "Value": "Jaipur"}, {"Insight": "Most affected transport mode", "Value": "Sea"}, {"Insight": "Top insurance claims (Origin-&gt;Destination)", "Value": "[{\"Origin City\": \"Bhubaneswar\", \"Destination City\": \"Gurugram\", \"Total Insurance Claim Amount\": 251969.5199999998}, {\"Origin City\": \"Ahmedabad\", \"Destination City\": \"Kochi\", \"Total Insurance Claim Amount\": 234142.12799999985}, {\"Origin City\": \"Chennai\", \"Destination City\": \"Visakhapatnam\", \"Total Insurance Claim Amount\": 192026.2739999998}, {\"Origin City\": \"Srinagar\", \"Destination City\": \"Chennai\", \"Total Insurance Claim Amount\": 186592.38399999985}, {\"Origin City\": \"Srinagar\", \"Destination City\": \"Pune\", \"Total Insurance Claim Amount\": 170290.5599999998}]"}, {"Insight": "Recovery opportunities (Origin-&gt;Destination)", "Value": "[{\"Origin City\": \"Bhubaneswar\", \"Destination City\": \"Gurugram\", \"Total Recovery Amount\": 251969.5199999998}, {\"Origin City\": \"Ahmedabad\", \"Destination City\": \"Kochi\", \"Total Recovery Amount\": 242664.87999999957}, {\"Origin City\": \"Srinagar\", \"Destination City\": \"Chennai\", \"Total Recovery Amount\": 197811.36799999975}, {\"Origin City\": \"Chennai\", \"Destination City\": \"Visakhapatnam\", \"Total Recovery Amount\": 192026.2739999998}, {\"Origin City\": \"Pune\", \"Destination City\": \"Chandigarh\", \"Total Recovery Amount\": 177586.5839999997}]"}, {"Insight": "Operational performance (Cold chain compliance %)", "Value": 79.62555066079295}, {"Insight": "Business health (Loss fraction of inventory)", "Value": 0.1062097488837984}, {"Insight": "Risk distribution", "Value": "{\"Medium Risk\": 595, \"Low Risk\": 176, \"High Risk\": 136, \"Critical Risk\": 1}"}, {"Insight": "Insurance threshold (Loss fraction)", "Value": 0.15}, {"Insight": "Recovery threshold (Loss fraction)", "Value": 0.07}]</t>
         </is>
       </c>
     </row>
